--- a/stories/arbres/ATOM-SEC.PAR.001-11.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-11.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Denis arrive au square avec papa. Papa montre la marelle. C'est l'espace montré. Denis saute dans les cases. Il sent le sol lisse. Papa s'assoit sur le banc. L'adulte voit Denis. Denis reste dans l'espace montré. Papa dit : je te vois. L'adulte voit. Plus tard, papa montre le jeu à ressort. Autre espace montré. Denis s'assoit dessus. Il revient au pied. Papa le voit encore. L'adulte voit. Même leçon, autre jeu. On reste dans l'espace montré. Maman arrivera après. Denis range son manteau sur le banc. Il reste là où papa a dit.</t>
+          <t>Denis arrive au square avec papa. Papa montre la marelle. C'est l'espace montré. Denis saute dans les cases. Il sent le sol lisse. Papa s'assoit sur le banc. L'adulte voit Denis. Denis reste dans l'espace montré. Je te vois. L'adulte voit. Plus tard, papa montre le jeu à ressort. Autre espace montré. Denis s'assoit dessus. Il revient au pied. Papa le voit encore. L'adulte voit. Même leçon, autre jeu. On reste dans l'espace montré. Maman arrivera après. Denis range son manteau sur le banc. Il reste là où papa a dit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Denis arrive au square avec papa. Papa montre la marelle. C'est l'espace montré. Denis saute dans les cases. Il sent le sol lisse. Papa s'assoit sur le banc. L'adulte voit Denis. Denis reste dans l'espace montré.
+papa|Je te vois. L'adulte voit. Plus tard, papa montre le jeu à ressort. Autre espace montré.
+narrateur|Denis s'assoit dessus. Il revient au pied. Papa le voit encore. L'adulte voit. Même leçon, autre jeu. On reste dans l'espace montré. Maman arrivera après. Denis range son manteau sur le banc. Il reste là où papa a dit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Denis joue au square. Où reste-t-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Denis est resté dans l'espace montré. À la marelle, puis au jeu à ressort. L'adulte voit.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Denis prend la main de papa. Ils quittent le square.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-11.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-11.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Denis s'assoit dessus. Il revient au pied. Papa le voit encore. L'adulte voit. Même leçon, autre jeu. On reste dans l'espace montré. Maman arrivera après. Denis range son manteau sur le banc. Il reste là où papa a dit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1501,7 @@
           <t>narrateur|Denis joue au square. Où reste-t-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1673,7 @@
           <t>narrateur|Denis est resté dans l'espace montré. À la marelle, puis au jeu à ressort. L'adulte voit.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1841,7 @@
           <t>narrateur|Denis prend la main de papa. Ils quittent le square.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2052,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2267,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.PAR.001-11.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-11.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Denis joue où papa voit</t>
+          <t>La marelle de Raphaël</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Raphaël saute à la marelle puis au jeu à ressort, dans l'espace que papa a montré.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Denis arrive au square avec papa. Papa montre la marelle. C'est l'espace montré. Denis saute dans les cases. Il sent le sol lisse. Papa s'assoit sur le banc. L'adulte voit Denis. Denis reste dans l'espace montré. Je te vois. L'adulte voit. Plus tard, papa montre le jeu à ressort. Autre espace montré. Denis s'assoit dessus. Il revient au pied. Papa le voit encore. L'adulte voit. Même leçon, autre jeu. On reste dans l'espace montré. Maman arrivera après. Denis range son manteau sur le banc. Il reste là où papa a dit.</t>
+          <t>Un caillou blanc dort dans une case. La marelle est dessinée à la craie. Le square sent le bitume tiède. Un manteau bleu est plié sur le banc. Une craie courte laisse un trait blanc. Papa pose le manteau. Tu as vu le caillou, Raphaël ? Oui, papa. Il est blanc. En ce moment, papa montre la marelle. C'est l'espace montré. Tu joues ici. L'adulte voit. Dans les cases ? Oui. On reste dans l'espace montré. Raphaël saute dans les cases. Il sent le sol lisse. Papa s'assoit sur le banc. L'adulte voit Raphaël. Raphaël reste dans l'espace montré. Je te vois. L'adulte voit. Tu me vois ? Oui. Le caillou saute d'une case à l'autre. Les pieds tapent, tout légers. Tu joues là où l'adulte a dit. Dans l'espace montré. Oui. Plus tard, papa montre le jeu à ressort. Autre espace montré. Ici, l'adulte voit encore. Je peux m'asseoir ? Oui. Tu restes dans l'espace montré. Raphaël s'assoit dessus. Le siège est un peu rêche. Ça penche, tout doux. Il revient au pied. Papa le voit encore. L'adulte voit. Tu restes là où l'adulte a dit ? Oui. Bravo, Raphaël. Tu as fait du bon travail. Raphaël range son manteau sur le banc. Le tissu bleu est un peu chaud. Il reste là où papa a dit. Il reste dans l'espace montré. Tu as fini de sauter ? Oui, papa. Bravo. Le caillou blanc reste dans une case. Raphaël le pose au milieu. Il dort. Oui. Dans l'espace montré. Une craie blanche marque encore le sol. Raphaël reste près du banc. L'adulte voit. Le jeu à ressort s'arrête, tout doux. Raphaël pose la main sur le siège. C'est rêche. Oui. Tu as sauté dans l'espace montré. Dans l'espace montré. Bravo.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,9 +1324,74 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Denis arrive au square avec papa. Papa montre la marelle. C'est l'espace montré. Denis saute dans les cases. Il sent le sol lisse. Papa s'assoit sur le banc. L'adulte voit Denis. Denis reste dans l'espace montré.
-papa|Je te vois. L'adulte voit. Plus tard, papa montre le jeu à ressort. Autre espace montré.
-narrateur|Denis s'assoit dessus. Il revient au pied. Papa le voit encore. L'adulte voit. Même leçon, autre jeu. On reste dans l'espace montré. Maman arrivera après. Denis range son manteau sur le banc. Il reste là où papa a dit.</t>
+          <t>narrateur|Un caillou blanc dort dans une case.
+narrateur|La marelle est dessinée à la craie.
+narrateur|Le square sent le bitume tiède.
+narrateur|Un manteau bleu est plié sur le banc.
+narrateur|Une craie courte laisse un trait blanc.
+narrateur|Papa pose le manteau.
+papa|Tu as vu le caillou, Raphaël ?
+enfant-m|Oui, papa.
+enfant-m|Il est blanc.
+narrateur|En ce moment, papa montre la marelle.
+papa|C'est l'espace montré.
+papa|Tu joues ici.
+papa|L'adulte voit.
+enfant-m|Dans les cases ?
+papa|Oui.
+papa|On reste dans l'espace montré.
+narrateur|Raphaël saute dans les cases.
+narrateur|Il sent le sol lisse.
+narrateur|Papa s'assoit sur le banc.
+narrateur|L'adulte voit Raphaël.
+narrateur|Raphaël reste dans l'espace montré.
+papa|Je te vois.
+papa|L'adulte voit.
+enfant-m|Tu me vois ?
+papa|Oui.
+narrateur|Le caillou saute d'une case à l'autre.
+narrateur|Les pieds tapent, tout légers.
+papa|Tu joues là où l'adulte a dit.
+enfant-m|Dans l'espace montré.
+papa|Oui.
+narrateur|Plus tard, papa montre le jeu à ressort.
+papa|Autre espace montré.
+papa|Ici, l'adulte voit encore.
+enfant-m|Je peux m'asseoir ?
+papa|Oui.
+papa|Tu restes dans l'espace montré.
+narrateur|Raphaël s'assoit dessus.
+narrateur|Le siège est un peu rêche.
+narrateur|Ça penche, tout doux.
+narrateur|Il revient au pied.
+narrateur|Papa le voit encore.
+narrateur|L'adulte voit.
+papa|Tu restes là où l'adulte a dit ?
+enfant-m|Oui.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|Raphaël range son manteau sur le banc.
+narrateur|Le tissu bleu est un peu chaud.
+narrateur|Il reste là où papa a dit.
+narrateur|Il reste dans l'espace montré.
+papa|Tu as fini de sauter ?
+enfant-m|Oui, papa.
+papa|Bravo.
+narrateur|Le caillou blanc reste dans une case.
+narrateur|Raphaël le pose au milieu.
+enfant-m|Il dort.
+papa|Oui.
+papa|Dans l'espace montré.
+narrateur|Une craie blanche marque encore le sol.
+narrateur|Raphaël reste près du banc.
+narrateur|L'adulte voit.
+narrateur|Le jeu à ressort s'arrête, tout doux.
+narrateur|Raphaël pose la main sur le siège.
+enfant-m|C'est rêche.
+papa|Oui.
+papa|Tu as sauté dans l'espace montré.
+enfant-m|Dans l'espace montré.
+papa|Bravo.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1342,7 +1419,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Denis joue au square. Où reste-t-il ?</t>
+          <t>Raphaël joue au square. Où reste-t-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1498,7 +1575,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Denis joue au square. Où reste-t-il ?</t>
+          <t>narrateur|Raphaël joue au square.
+narrateur|Où reste-t-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1526,7 +1604,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Denis est resté dans l'espace montré. À la marelle, puis au jeu à ressort. L'adulte voit.</t>
+          <t>Raphaël est resté dans l'espace montré. À la marelle, puis au jeu à ressort. L'adulte voit. Tu es resté dans l'espace montré ? Oui. À la marelle, puis au ressort. Bravo. L'adulte voit. La craie laisse encore un trait blanc.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1670,7 +1748,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Denis est resté dans l'espace montré. À la marelle, puis au jeu à ressort. L'adulte voit.</t>
+          <t>narrateur|Raphaël est resté dans l'espace montré.
+narrateur|À la marelle, puis au jeu à ressort.
+narrateur|L'adulte voit.
+papa|Tu es resté dans l'espace montré ?
+enfant-m|Oui.
+enfant-m|À la marelle, puis au ressort.
+papa|Bravo.
+papa|L'adulte voit.
+narrateur|La craie laisse encore un trait blanc.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1698,7 +1784,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Denis prend la main de papa. Ils quittent le square.</t>
+          <t>Raphaël prend la main de papa. Tu as fini de ranger le manteau ? Oui, papa. Bravo. Maman arrive près du square. Vous avez joué ici ? Oui, maman. Dans l'espace montré. L'adulte voit. Ils quittent le square. Le bitume reste tiède.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1838,7 +1924,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Denis prend la main de papa. Ils quittent le square.</t>
+          <t>narrateur|Raphaël prend la main de papa.
+papa|Tu as fini de ranger le manteau ?
+enfant-m|Oui, papa.
+papa|Bravo.
+narrateur|Maman arrive près du square.
+maman|Vous avez joué ici ?
+enfant-m|Oui, maman.
+papa|Dans l'espace montré.
+maman|L'adulte voit.
+narrateur|Ils quittent le square.
+narrateur|Le bitume reste tiède.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1866,7 +1962,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le caillou blanc dort encore. On a sauté. Oui. Dans l'espace montré. Bravo, Raphaël. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2006,7 +2102,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le caillou blanc dort encore.
+enfant-m|On a sauté.
+papa|Oui.
+papa|Dans l'espace montré.
+papa|Bravo, Raphaël.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2028,7 +2129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2066,6 +2167,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-11.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-11.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un caillou blanc dort dans une case. La marelle est dessinée à la craie. Le square sent le bitume tiède. Un manteau bleu est plié sur le banc. Une craie courte laisse un trait blanc. Papa pose le manteau. Tu as vu le caillou, Raphaël ? Oui, papa. Il est blanc. En ce moment, papa montre la marelle. C'est l'espace montré. Tu joues ici. L'adulte voit. Dans les cases ? Oui. On reste dans l'espace montré. Raphaël saute dans les cases. Il sent le sol lisse. Papa s'assoit sur le banc. L'adulte voit Raphaël. Raphaël reste dans l'espace montré. Je te vois. L'adulte voit. Tu me vois ? Oui. Le caillou saute d'une case à l'autre. Les pieds tapent, tout légers. Tu joues là où l'adulte a dit. Dans l'espace montré. Oui. Plus tard, papa montre le jeu à ressort. Autre espace montré. Ici, l'adulte voit encore. Je peux m'asseoir ? Oui. Tu restes dans l'espace montré. Raphaël s'assoit dessus. Le siège est un peu rêche. Ça penche, tout doux. Il revient au pied. Papa le voit encore. L'adulte voit. Tu restes là où l'adulte a dit ? Oui. Bravo, Raphaël. Tu as fait du bon travail. Raphaël range son manteau sur le banc. Le tissu bleu est un peu chaud. Il reste là où papa a dit. Il reste dans l'espace montré. Tu as fini de sauter ? Oui, papa. Bravo. Le caillou blanc reste dans une case. Raphaël le pose au milieu. Il dort. Oui. Dans l'espace montré. Une craie blanche marque encore le sol. Raphaël reste près du banc. L'adulte voit. Le jeu à ressort s'arrête, tout doux. Raphaël pose la main sur le siège. C'est rêche. Oui. Tu as sauté dans l'espace montré. Dans l'espace montré. Bravo.</t>
+          <t>Un caillou blanc dort dans une case. La marelle est dessinée à la craie. Le square sent le bitume tiède. Un manteau bleu est plié sur le banc. Une craie courte laisse un trait blanc. Papa pose le manteau. Tu as vu le caillou, Raphaël ? Oui, papa. Il est blanc. En ce moment, papa montre la marelle. C'est l'espace montré. Tu joues ici. L'adulte voit. Dans les cases ? Oui. On reste dans l'espace montré. Raphaël saute dans les cases. Il sent le sol lisse. Papa s'assoit sur le banc. L'adulte voit Raphaël. Raphaël reste dans l'espace montré. Je te vois. L'adulte voit. Tu me vois ? Oui. Le caillou saute d'une case à l'autre. Les pieds tapent, tout légers. Tu joues là où l'adulte a dit. Dans l'espace montré. Oui. Plus tard, papa montre le jeu à ressort. Autre espace montré. Ici, l'adulte voit encore. Je peux m'asseoir ? Oui. Tu restes dans l'espace montré. Raphaël s'assoit dessus. Le siège est un peu rêche. Ça penche, tout doux. Il revient au pied. Papa le voit encore. L'adulte voit. Tu restes là où l'adulte a dit ? Oui. Bravo, Raphaël. Raphaël range son manteau sur le banc. Le tissu bleu est un peu chaud. Il reste là où papa a dit. Il reste dans l'espace montré. Tu as fini de sauter ? Oui, papa. Bravo. Le caillou blanc reste dans une case. Raphaël le pose au milieu. Il dort. Oui. Dans l'espace montré. Une craie blanche marque encore le sol. Raphaël reste près du banc. L'adulte voit. Le jeu à ressort s'arrête, tout doux. Raphaël pose la main sur le siège. C'est rêche. Oui. Tu as sauté dans l'espace montré. Dans l'espace montré. Bravo.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Denis arrive au square avec papa. Papa montre la marelle. C'est l'&lt;emphasis level="moderate"&gt;espace&lt;/emphasis&gt; montré. Denis saute dans les cases. Il sent le sol lisse. Papa s'assoit sur le banc. L'adulte voit Denis. Denis reste dans l'espace montré. Papa dit : je te vois. L'adulte voit. Plus tard, papa montre le jeu à ressort. Autre espace montré. Denis s'assoit dessus. Il revient au pied. Papa le voit encore. L'adulte voit. Même leçon, autre jeu. On reste dans l'espace montré. Maman arrivera après. Denis range son manteau sur le banc. Il reste là où papa a dit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un caillou blanc dort dans une case. La marelle est dessinée à la craie. Le square sent le bitume tiède. Un manteau bleu est plié sur le banc. Une craie courte laisse un trait blanc. Papa pose le manteau. Tu as vu le caillou, Raphaël ? Oui, papa. Il est blanc. En ce moment, papa montre la marelle. C'est l'espace montré. Tu joues ici. L'adulte voit. Dans les cases ? Oui. On reste dans l'espace montré. Raphaël saute dans les cases. Il sent le sol lisse. Papa s'assoit sur le banc. L'adulte voit Raphaël. Raphaël reste dans l'espace montré. Je te vois. L'adulte voit. Tu me vois ? Oui. Le caillou saute d'une case à l'autre. Les pieds tapent, tout légers. Tu joues là où l'adulte a dit. Dans l'espace montré. Oui. Plus tard, papa montre le jeu à ressort. Autre espace montré. Ici, l'adulte voit encore. Je peux m'asseoir ? Oui. Tu restes dans l'espace montré. Raphaël s'assoit dessus. Le siège est un peu rêche. Ça penche, tout doux. Il revient au pied. Papa le voit encore. L'adulte voit. Tu restes là où l'adulte a dit ? Oui. Bravo, Raphaël. Raphaël range son manteau sur le banc. Le tissu bleu est un peu chaud. Il reste là où papa a dit. Il reste dans l'espace montré. Tu as fini de sauter ? Oui, papa. Bravo. Le caillou blanc reste dans une case. Raphaël le pose au milieu. Il dort. Oui. Dans l'espace montré. Une craie blanche marque encore le sol. Raphaël reste près du banc. L'adulte voit. Le jeu à ressort s'arrête, tout doux. Raphaël pose la main sur le siège. C'est rêche. Oui. Tu as sauté dans l'espace montré. Dans l'espace montré. Bravo.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1369,7 +1369,6 @@
 papa|Tu restes là où l'adulte a dit ?
 enfant-m|Oui.
 papa|Bravo, Raphaël.
-papa|Tu as fait du bon travail.
 narrateur|Raphaël range son manteau sur le banc.
 narrateur|Le tissu bleu est un peu chaud.
 narrateur|Il reste là où papa a dit.
@@ -1394,7 +1393,6 @@
 papa|Bravo.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1424,7 +1422,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Denis joue au square. Où reste-t-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël joue au square. Où reste-t-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1579,7 +1577,6 @@
 narrateur|Où reste-t-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1609,7 +1606,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Denis est resté dans l'&lt;emphasis level="moderate"&gt;espace&lt;/emphasis&gt; montré. À la marelle, puis au jeu à ressort. L'adulte voit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël est resté dans l'espace montré. À la marelle, puis au jeu à ressort. L'adulte voit. Tu es resté dans l'espace montré ? Oui. À la marelle, puis au ressort. Bravo. L'adulte voit. La craie laisse encore un trait blanc.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1759,7 +1756,6 @@
 narrateur|La craie laisse encore un trait blanc.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1789,7 +1785,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Denis prend la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; de papa. Ils quittent le square.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël prend la main de papa. Tu as fini de ranger le manteau ? Oui, papa. Bravo. Maman arrive près du square. Vous avez joué ici ? Oui, maman. Dans l'espace montré. L'adulte voit. Ils quittent le square. Le bitume reste tiède.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1937,7 +1933,6 @@
 narrateur|Le bitume reste tiède.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1962,12 +1957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le caillou blanc dort encore. On a sauté. Oui. Dans l'espace montré. Bravo, Raphaël. L'histoire est finie.</t>
+          <t>Le caillou blanc dort encore. On a sauté. Oui. Dans l'espace montré. Bravo, Raphaël.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le caillou blanc dort encore. On a sauté. Oui. Dans l'espace montré. Bravo, Raphaël.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2106,11 +2101,9 @@
 enfant-m|On a sauté.
 papa|Oui.
 papa|Dans l'espace montré.
-papa|Bravo, Raphaël.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+papa|Bravo, Raphaël.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2129,7 +2122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2174,6 +2167,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-11.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-11.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Denis, papa, maman</t>
+          <t>Raphaël, papa, maman</t>
         </is>
       </c>
     </row>
